--- a/data/trans_dic/P37A$vacunaempresa-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunaempresa-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,15</t>
+          <t>0,33; 2,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,06</t>
+          <t>0,28; 2,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,5</t>
+          <t>0,15; 1,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,59</t>
+          <t>0,64; 2,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,54</t>
+          <t>0,27; 1,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,68</t>
+          <t>0,19; 1,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,08</t>
+          <t>1,83; 4,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,58</t>
+          <t>0,42; 1,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,42</t>
+          <t>0,38; 1,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,96</t>
+          <t>0,2; 0,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,84</t>
+          <t>1,42; 3,03</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,06</t>
+          <t>0,64; 1,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,15</t>
+          <t>0,59; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,39</t>
+          <t>0,27; 1,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,96</t>
+          <t>1,46; 3,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,32</t>
+          <t>0,3; 1,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,44</t>
+          <t>0,37; 1,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,61</t>
+          <t>2,16; 4,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,42</t>
+          <t>0,51; 1,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,65</t>
+          <t>0,64; 1,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,14</t>
+          <t>0,4; 1,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,32</t>
+          <t>2,05; 3,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,76</t>
+          <t>0,26; 1,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,38</t>
+          <t>0,4; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,87</t>
+          <t>1,46; 3,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,45</t>
+          <t>0,14; 1,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,51</t>
+          <t>0,62; 2,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,33</t>
+          <t>0,14; 1,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,97</t>
+          <t>1,17; 2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,19</t>
+          <t>0,34; 1,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,91</t>
+          <t>0,61; 1,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,74</t>
+          <t>0,12; 0,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,95</t>
+          <t>1,61; 3,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,03</t>
+          <t>0,65; 1,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,47</t>
+          <t>1,4; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,21</t>
+          <t>0,12; 1,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,6</t>
+          <t>2,94; 5,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,87</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,29</t>
+          <t>0,24; 1,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,25</t>
+          <t>0,17; 1,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,85</t>
+          <t>3,52; 5,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,17</t>
+          <t>0,45; 1,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,07</t>
+          <t>0,93; 2,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,89</t>
+          <t>0,23; 0,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,27</t>
+          <t>3,51; 5,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,47</t>
+          <t>0,75; 1,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,78</t>
+          <t>0,26; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,2</t>
+          <t>2,18; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,84</t>
+          <t>0,33; 0,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,23</t>
+          <t>0,58; 1,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,84</t>
+          <t>0,32; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,54</t>
+          <t>2,7; 3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,99</t>
+          <t>0,59; 1,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,41</t>
+          <t>0,87; 1,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,69</t>
+          <t>0,34; 0,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,28</t>
+          <t>2,57; 3,38</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26914</t>
+          <t>29416</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2180; 14929</t>
+          <t>2308; 15809</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2145; 14519</t>
+          <t>2001; 14717</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>998; 10092</t>
+          <t>1000; 9828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3841; 16441</t>
+          <t>4455; 17735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1850; 10575</t>
+          <t>1868; 10518</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1131; 11697</t>
+          <t>1356; 11298</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6684</t>
+          <t>0; 7626</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12220; 29584</t>
+          <t>13455; 30294</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5641; 21825</t>
+          <t>5818; 20986</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5106; 19879</t>
+          <t>5284; 20254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1965; 12985</t>
+          <t>2736; 12437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17722; 38677</t>
+          <t>20179; 43129</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54455</t>
+          <t>56255</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6164; 19771</t>
+          <t>6118; 19138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5982; 21845</t>
+          <t>5999; 22143</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2706; 14241</t>
+          <t>2780; 15599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10267; 35335</t>
+          <t>15350; 34634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2921; 12770</t>
+          <t>2876; 13186</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4970; 19259</t>
+          <t>4938; 19302</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3048; 14966</t>
+          <t>3814; 15387</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22777; 44172</t>
+          <t>23126; 44398</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10618; 27476</t>
+          <t>9926; 27305</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13603; 33810</t>
+          <t>13031; 34708</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7658; 23610</t>
+          <t>8199; 24346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36580; 71504</t>
+          <t>43543; 70655</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>36184</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024; 11969</t>
+          <t>1746; 10651</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3143; 18003</t>
+          <t>3057; 16224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5643</t>
+          <t>0; 5428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12532; 34341</t>
+          <t>11696; 31672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>933; 9939</t>
+          <t>974; 9511</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4818; 19514</t>
+          <t>4838; 20245</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>991; 10442</t>
+          <t>1084; 9957</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4799; 18395</t>
+          <t>9468; 23239</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4695; 16174</t>
+          <t>4620; 17054</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9982; 29292</t>
+          <t>9291; 28848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1981; 11444</t>
+          <t>1882; 11612</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19479; 48388</t>
+          <t>25946; 50945</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48750</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>90353</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6198; 19136</t>
+          <t>6108; 18522</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13053; 32920</t>
+          <t>13229; 33463</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1128; 11322</t>
+          <t>1118; 10948</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27596; 51932</t>
+          <t>29119; 54698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>980; 9004</t>
+          <t>978; 8858</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2578; 13550</t>
+          <t>2555; 13918</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1817; 13019</t>
+          <t>1818; 12467</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36241; 64088</t>
+          <t>39359; 62981</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8499; 23204</t>
+          <t>8845; 23947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18542; 41391</t>
+          <t>18577; 40507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4549; 17558</t>
+          <t>4533; 18952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70321; 106489</t>
+          <t>74099; 108589</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24270; 48014</t>
+          <t>24584; 48567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34617; 64547</t>
+          <t>34748; 64513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9042; 26472</t>
+          <t>8886; 25994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67409; 110563</t>
+          <t>77178; 116429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11597; 28389</t>
+          <t>10996; 28172</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21545; 43891</t>
+          <t>20789; 44556</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11815; 29907</t>
+          <t>11466; 28883</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>86964; 131265</t>
+          <t>100735; 139588</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39283; 66045</t>
+          <t>39214; 68139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60565; 98393</t>
+          <t>61116; 100264</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23057; 47937</t>
+          <t>23846; 49113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>170575; 235060</t>
+          <t>187093; 245828</t>
         </is>
       </c>
     </row>
